--- a/从零开始学Slots/从零开始学Slots-34-番外篇-Python读取数据表.xlsx
+++ b/从零开始学Slots/从零开始学Slots-34-番外篇-Python读取数据表.xlsx
@@ -5791,6 +5791,9 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
+  <ignoredErrors>
+    <ignoredError sqref="A1:N146" evalError="1" twoDigitTextYear="1" numberStoredAsText="1" formula="1" formulaRange="1" unlockedFormula="1" emptyCellReference="1" listDataValidation="1" calculatedColumn="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
@@ -6306,5 +6309,8 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
+  <ignoredErrors>
+    <ignoredError sqref="A1:M63" evalError="1" twoDigitTextYear="1" numberStoredAsText="1" formula="1" formulaRange="1" unlockedFormula="1" emptyCellReference="1" listDataValidation="1" calculatedColumn="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
--- a/从零开始学Slots/从零开始学Slots-34-番外篇-Python读取数据表.xlsx
+++ b/从零开始学Slots/从零开始学Slots-34-番外篇-Python读取数据表.xlsx
@@ -4614,10 +4614,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="0.00%"/>
     <numFmt numFmtId="166" formatCode="#,##0"/>
+    <numFmt numFmtId="167" formatCode="0.0000000000%"/>
   </numFmts>
   <fonts count="16">
     <font>
@@ -4788,7 +4789,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="33">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -4911,6 +4912,14 @@
     </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" applyNumberFormat="1" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" applyNumberFormat="1" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -6077,7 +6086,7 @@
       <c r="B26" s="20" t="n">
         <v>0.3</v>
       </c>
-      <c r="C26" s="21" t="n">
+      <c r="C26" s="32" t="n">
         <f aca="false">SUM($B$26:B26)</f>
         <v>0.3</v>
       </c>
@@ -6092,7 +6101,7 @@
       <c r="B27" s="20" t="n">
         <v>0.5</v>
       </c>
-      <c r="C27" s="21" t="n">
+      <c r="C27" s="32" t="n">
         <f aca="false">SUM($B$26:B27)</f>
         <v>0.8</v>
       </c>
@@ -6107,7 +6116,7 @@
       <c r="B28" s="20" t="n">
         <v>0.2</v>
       </c>
-      <c r="C28" s="21" t="n">
+      <c r="C28" s="32" t="n">
         <f aca="false">SUM($B$26:B28)</f>
         <v>1</v>
       </c>
@@ -6119,11 +6128,11 @@
       <c r="A29" s="22" t="s">
         <v>158</v>
       </c>
-      <c r="B29" s="21" t="n">
+      <c r="B29" s="32" t="n">
         <f aca="false">SUM(B26:B28)</f>
         <v>1</v>
       </c>
-      <c r="C29" s="21" t="n">
+      <c r="C29" s="32" t="n">
         <f aca="false">C28</f>
         <v>1</v>
       </c>
